--- a/forms/trg/Formulir_TRG_dfd-rg.xlsx
+++ b/forms/trg/Formulir_TRG_dfd-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B21)</f>
+        <f>COUNTA(Anggota!B5:B22)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F21)</f>
+        <f>COUNTA(Anggota!F5:F22)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,27 +913,35 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Fuad Husain Akbar., drg., MARS., Ph.D., FISQua</t>
+          <t>Prof. Dr. Hasanuddin Thahir., drg., MS., Sp.Perio(K)</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturer</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>orcid-search/search?searchQuery=hasanuddin%20thahir</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6018203</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57200224347</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -946,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. dr. Husnul Mubarak., Sp. KFR</t>
+          <t>Prof. Fuad Husain Akbar., drg., MARS., Ph.D., FISQua</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -979,12 +987,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin., M.Sc</t>
+          <t>Dr. dr. Husnul Mubarak., Sp. KFR</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1012,18 +1020,18 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>DR. NOR ATIKA BINTI MD ASHAR</t>
+          <t>Hasanuddin., M.Sc</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1045,18 +1053,18 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Alif Musakkir</t>
+          <t>DR. NOR ATIKA BINTI MD ASHAR</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Graduate Student</t>
+          <t>External Collaborator</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1076,10 +1084,26 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Alif Musakkir</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Graduate Student</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>DFDIG serves as a collaborative platform that unites expertise in dentistry, information technology, biomedical science, and forensic studies. The group aims to develop intelligent systems and ethical frameworks that ensure the reliability, safety, and legal admissibility of digital dental data. Through interdisciplinary research and global partnerships, DFDIG aspires to contribute significantly to the development of national and regional policies in digital forensic dentistry, aligning with Indonesia’s National Research Priorities (PRN) on health technology and artificial intelligence.</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1087,7 +1111,11 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1276,15 +1304,32 @@
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="12" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
